--- a/diseases/d010/2000-2004.xlsx
+++ b/diseases/d010/2000-2004.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
@@ -1457,9 +1454,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
@@ -2001,9 +1995,6 @@
       <c r="O9" t="n">
         <v>0</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
@@ -2545,9 +2536,6 @@
       <c r="O12" t="n">
         <v>0</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
@@ -3089,9 +3077,6 @@
       <c r="O15" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
@@ -3633,9 +3618,6 @@
       <c r="O18" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
@@ -4177,9 +4159,6 @@
       <c r="O21" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>0</v>
       </c>
@@ -4721,9 +4700,6 @@
       <c r="O24" t="n">
         <v>2</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0.03863837217310803</v>
       </c>
@@ -5265,9 +5241,6 @@
       <c r="O27" t="n">
         <v>0</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
@@ -5809,9 +5782,6 @@
       <c r="O30" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
@@ -6353,9 +6323,6 @@
       <c r="O33" t="n">
         <v>1</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>0.01931918608655401</v>
       </c>
@@ -6897,9 +6864,6 @@
       <c r="O36" t="n">
         <v>0</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0</v>
       </c>
@@ -7441,9 +7405,6 @@
       <c r="O39" t="n">
         <v>1</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>0.01927535832409241</v>
       </c>
@@ -7985,9 +7946,6 @@
       <c r="O42" t="n">
         <v>0</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0</v>
       </c>
@@ -8529,9 +8487,6 @@
       <c r="O45" t="n">
         <v>0</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>0</v>
       </c>
@@ -9073,9 +9028,6 @@
       <c r="O48" t="n">
         <v>0</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0</v>
       </c>
@@ -9617,9 +9569,6 @@
       <c r="O51" t="n">
         <v>0</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0</v>
       </c>
@@ -10161,9 +10110,6 @@
       <c r="O54" t="n">
         <v>0</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0</v>
       </c>
@@ -10705,9 +10651,6 @@
       <c r="O57" t="n">
         <v>0</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0</v>
       </c>
@@ -11249,9 +11192,6 @@
       <c r="O60" t="n">
         <v>0</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0</v>
       </c>
@@ -11793,9 +11733,6 @@
       <c r="O63" t="n">
         <v>0</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0</v>
       </c>
@@ -12337,9 +12274,6 @@
       <c r="O66" t="n">
         <v>1</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0.01927535832409241</v>
       </c>
@@ -12881,9 +12815,6 @@
       <c r="O69" t="n">
         <v>0</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0</v>
       </c>
@@ -13425,9 +13356,6 @@
       <c r="O72" t="n">
         <v>0</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0</v>
       </c>
@@ -13969,9 +13897,6 @@
       <c r="O75" t="n">
         <v>0</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>0</v>
       </c>
@@ -14513,9 +14438,6 @@
       <c r="O78" t="n">
         <v>0</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0</v>
       </c>
@@ -15057,9 +14979,6 @@
       <c r="O81" t="n">
         <v>0</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>0</v>
       </c>
@@ -15601,9 +15520,6 @@
       <c r="O84" t="n">
         <v>0</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0</v>
       </c>
@@ -16145,9 +16061,6 @@
       <c r="O87" t="n">
         <v>0</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" t="n">
         <v>0</v>
       </c>
@@ -16689,9 +16602,6 @@
       <c r="O90" t="n">
         <v>0</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0</v>
       </c>
@@ -17233,9 +17143,6 @@
       <c r="O93" t="n">
         <v>0</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0</v>
       </c>
@@ -17777,9 +17684,6 @@
       <c r="O96" t="n">
         <v>0</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0</v>
       </c>
@@ -18321,9 +18225,6 @@
       <c r="O99" t="n">
         <v>0</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0</v>
       </c>
@@ -18865,9 +18766,6 @@
       <c r="O102" t="n">
         <v>0</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0</v>
       </c>
@@ -19409,9 +19307,6 @@
       <c r="O105" t="n">
         <v>1</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0.01922875021199697</v>
       </c>
@@ -19953,9 +19848,6 @@
       <c r="O108" t="n">
         <v>0</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0</v>
       </c>
@@ -20497,9 +20389,6 @@
       <c r="O111" t="n">
         <v>0</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0</v>
       </c>
@@ -21189,9 +21078,6 @@
       <c r="O115" t="n">
         <v>0</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0</v>
       </c>
@@ -21881,9 +21767,6 @@
       <c r="O119" t="n">
         <v>0</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0</v>
       </c>
@@ -22425,9 +22308,6 @@
       <c r="O122" t="n">
         <v>0</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0</v>
       </c>
@@ -23117,9 +22997,6 @@
       <c r="O126" t="n">
         <v>1</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>0.01918297779282576</v>
       </c>
@@ -23661,9 +23538,6 @@
       <c r="O129" t="n">
         <v>1</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="R129" t="n">
         <v>0.01918297779282576</v>
       </c>
@@ -24353,9 +24227,6 @@
       <c r="O133" t="n">
         <v>0</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="R133" t="n">
         <v>0</v>
       </c>
@@ -24897,9 +24768,6 @@
       <c r="O136" t="n">
         <v>0</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0</v>
       </c>
@@ -25589,9 +25457,6 @@
       <c r="O140" t="n">
         <v>0</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>0</v>
       </c>
@@ -26281,9 +26146,6 @@
       <c r="O144" t="n">
         <v>0</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="R144" t="n">
         <v>0</v>
       </c>
@@ -26973,9 +26835,6 @@
       <c r="O148" t="n">
         <v>0</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>0</v>
       </c>
@@ -27517,9 +27376,6 @@
       <c r="O151" t="n">
         <v>0</v>
       </c>
-      <c r="Q151" t="n">
-        <v>0</v>
-      </c>
       <c r="R151" t="n">
         <v>0</v>
       </c>
@@ -28209,9 +28065,6 @@
       <c r="O155" t="n">
         <v>0</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="R155" t="n">
         <v>0</v>
       </c>
@@ -28901,9 +28754,6 @@
       <c r="O159" t="n">
         <v>0</v>
       </c>
-      <c r="Q159" t="n">
-        <v>0</v>
-      </c>
       <c r="R159" t="n">
         <v>0</v>
       </c>
@@ -29593,9 +29443,6 @@
       <c r="O163" t="n">
         <v>0</v>
       </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
       <c r="R163" t="n">
         <v>0</v>
       </c>
@@ -30137,9 +29984,6 @@
       <c r="O166" t="n">
         <v>0</v>
       </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
       <c r="R166" t="n">
         <v>0</v>
       </c>
@@ -30829,9 +30673,6 @@
       <c r="O170" t="n">
         <v>0</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="R170" t="n">
         <v>0</v>
       </c>
@@ -31373,9 +31214,6 @@
       <c r="O173" t="n">
         <v>0</v>
       </c>
-      <c r="Q173" t="n">
-        <v>0</v>
-      </c>
       <c r="R173" t="n">
         <v>0</v>
       </c>
@@ -31917,9 +31755,6 @@
       <c r="O176" t="n">
         <v>0</v>
       </c>
-      <c r="Q176" t="n">
-        <v>0</v>
-      </c>
       <c r="R176" t="n">
         <v>0</v>
       </c>
@@ -32609,9 +32444,6 @@
       <c r="O180" t="n">
         <v>1</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>0.01912723205234435</v>
       </c>
@@ -33153,9 +32985,6 @@
       <c r="O183" t="n">
         <v>0</v>
       </c>
-      <c r="Q183" t="n">
-        <v>0</v>
-      </c>
       <c r="R183" t="n">
         <v>0</v>
       </c>
@@ -33697,9 +33526,6 @@
       <c r="O186" t="n">
         <v>0</v>
       </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
       <c r="R186" t="n">
         <v>0</v>
       </c>
@@ -34389,9 +34215,6 @@
       <c r="O190" t="n">
         <v>0</v>
       </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
       <c r="R190" t="n">
         <v>0</v>
       </c>
@@ -34931,9 +34754,6 @@
         <v>0</v>
       </c>
       <c r="O193" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q193" t="n">
         <v>0</v>
       </c>
       <c r="R193" t="n">
